--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestorsHoldInfoRegistAll.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestorsHoldInfoRegistAll.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20736" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="投资者持有信息登记" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
   <si>
     <t>2.必填要素请参照《数据元规范》。</t>
   </si>
@@ -708,6 +708,10 @@
     <t>折算人民币金额（元）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -716,7 +720,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1212,7 +1216,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1220,20 +1224,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O32"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="18.625" style="17" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="15.625" style="17" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.25" style="17" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="18.375" style="17" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="17.125" style="17" customWidth="1" collapsed="1"/>
-    <col min="12" max="13" width="13.875" style="17" customWidth="1" collapsed="1"/>
+    <col min="1" max="7" width="18.6640625" style="17" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="15.6640625" style="17" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.21875" style="17" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="18.33203125" style="17" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="17.109375" style="17" customWidth="1" collapsed="1"/>
+    <col min="12" max="13" width="13.88671875" style="17" customWidth="1" collapsed="1"/>
     <col min="14" max="14" width="21" style="17" customWidth="1" collapsed="1"/>
     <col min="15" max="15" width="21" style="14" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="13.5" customHeight="1">
+    <row r="1" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>187</v>
       </c>
@@ -1278,98 +1282,10 @@
       </c>
       <c r="O1"/>
     </row>
-    <row r="2" spans="1:15">
-      <c r="O2"/>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="O3"/>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="O4"/>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="O5"/>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="O6"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="O7"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="O8"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="O9"/>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="O10"/>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="O11"/>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="O12"/>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="O13"/>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="O14"/>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="O15"/>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="O16"/>
-    </row>
-    <row r="17" spans="15:15">
-      <c r="O17"/>
-    </row>
-    <row r="18" spans="15:15">
-      <c r="O18"/>
-    </row>
-    <row r="19" spans="15:15">
-      <c r="O19"/>
-    </row>
-    <row r="20" spans="15:15">
-      <c r="O20"/>
-    </row>
-    <row r="21" spans="15:15">
-      <c r="O21"/>
-    </row>
-    <row r="22" spans="15:15">
-      <c r="O22"/>
-    </row>
-    <row r="23" spans="15:15">
-      <c r="O23"/>
-    </row>
-    <row r="24" spans="15:15">
-      <c r="O24"/>
-    </row>
-    <row r="25" spans="15:15">
-      <c r="O25"/>
-    </row>
-    <row r="26" spans="15:15">
-      <c r="O26"/>
-    </row>
-    <row r="27" spans="15:15">
-      <c r="O27"/>
-    </row>
-    <row r="28" spans="15:15">
-      <c r="O28"/>
-    </row>
-    <row r="29" spans="15:15">
-      <c r="O29"/>
-    </row>
-    <row r="30" spans="15:15">
-      <c r="O30"/>
-    </row>
-    <row r="31" spans="15:15">
-      <c r="O31"/>
-    </row>
-    <row r="32" spans="15:15">
-      <c r="O32"/>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>201</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1381,1378 +1297,1378 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A335"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="82.625" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="82.6640625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="48" customHeight="1">
+    <row r="1" spans="1:1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="37.5" customHeight="1">
+    <row r="2" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="23.25" customHeight="1">
+    <row r="3" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="14.25">
+    <row r="4" spans="1:1" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="103" spans="1:1">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="104" spans="1:1">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="105" spans="1:1">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="106" spans="1:1">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:1">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="109" spans="1:1">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="110" spans="1:1">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="111" spans="1:1">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="112" spans="1:1">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="113" spans="1:1">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="114" spans="1:1">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="115" spans="1:1">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="116" spans="1:1">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="117" spans="1:1">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="118" spans="1:1">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="119" spans="1:1">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="120" spans="1:1">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="121" spans="1:1">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="122" spans="1:1">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="123" spans="1:1">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="124" spans="1:1">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="125" spans="1:1">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="126" spans="1:1">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="127" spans="1:1">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="128" spans="1:1">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="129" spans="1:1">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="130" spans="1:1">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="131" spans="1:1">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="132" spans="1:1">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="133" spans="1:1">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="134" spans="1:1">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="135" spans="1:1">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="136" spans="1:1">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="137" spans="1:1">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="138" spans="1:1">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="139" spans="1:1">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="140" spans="1:1">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="141" spans="1:1">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="142" spans="1:1">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="143" spans="1:1">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="144" spans="1:1">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="145" spans="1:1">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="146" spans="1:1">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="147" spans="1:1">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="148" spans="1:1">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="149" spans="1:1">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="150" spans="1:1">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="151" spans="1:1">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="152" spans="1:1">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="153" spans="1:1">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="154" spans="1:1">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="155" spans="1:1">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="156" spans="1:1">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="157" spans="1:1">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="158" spans="1:1">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="159" spans="1:1">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="160" spans="1:1">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="161" spans="1:1">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="162" spans="1:1">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="163" spans="1:1">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="164" spans="1:1">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="165" spans="1:1">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="166" spans="1:1">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="167" spans="1:1">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="168" spans="1:1">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="169" spans="1:1">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="170" spans="1:1">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="171" spans="1:1">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="172" spans="1:1">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="173" spans="1:1">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="174" spans="1:1">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="175" spans="1:1">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="176" spans="1:1">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="177" spans="1:1">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="178" spans="1:1">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="179" spans="1:1">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="180" spans="1:1">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="181" spans="1:1">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="182" spans="1:1">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="183" spans="1:1">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="184" spans="1:1">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="12"/>
     </row>
-    <row r="185" spans="1:1">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="12"/>
     </row>
-    <row r="186" spans="1:1">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="12"/>
     </row>
-    <row r="187" spans="1:1">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="12"/>
     </row>
-    <row r="188" spans="1:1">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="12"/>
     </row>
-    <row r="189" spans="1:1">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="12"/>
     </row>
-    <row r="190" spans="1:1">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="12"/>
     </row>
-    <row r="191" spans="1:1">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="12"/>
     </row>
-    <row r="192" spans="1:1">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="12"/>
     </row>
-    <row r="193" spans="1:1">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="12"/>
     </row>
-    <row r="194" spans="1:1">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="12"/>
     </row>
-    <row r="195" spans="1:1">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="12"/>
     </row>
-    <row r="196" spans="1:1">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="12"/>
     </row>
-    <row r="197" spans="1:1">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="12"/>
     </row>
-    <row r="198" spans="1:1">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="12"/>
     </row>
-    <row r="199" spans="1:1">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="12"/>
     </row>
-    <row r="200" spans="1:1">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="12"/>
     </row>
-    <row r="201" spans="1:1">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="12"/>
     </row>
-    <row r="202" spans="1:1">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" s="12"/>
     </row>
-    <row r="203" spans="1:1">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" s="12"/>
     </row>
-    <row r="204" spans="1:1">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" s="12"/>
     </row>
-    <row r="205" spans="1:1">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205" s="12"/>
     </row>
-    <row r="206" spans="1:1">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" s="12"/>
     </row>
-    <row r="207" spans="1:1">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" s="12"/>
     </row>
-    <row r="208" spans="1:1">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" s="12"/>
     </row>
-    <row r="209" spans="1:1">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" s="12"/>
     </row>
-    <row r="210" spans="1:1">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" s="12"/>
     </row>
-    <row r="211" spans="1:1">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" s="12"/>
     </row>
-    <row r="212" spans="1:1">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" s="12"/>
     </row>
-    <row r="213" spans="1:1">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" s="12"/>
     </row>
-    <row r="214" spans="1:1">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" s="12"/>
     </row>
-    <row r="215" spans="1:1">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" s="12"/>
     </row>
-    <row r="216" spans="1:1">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" s="12"/>
     </row>
-    <row r="217" spans="1:1">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" s="12"/>
     </row>
-    <row r="218" spans="1:1">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" s="12"/>
     </row>
-    <row r="219" spans="1:1">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" s="12"/>
     </row>
-    <row r="220" spans="1:1">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" s="12"/>
     </row>
-    <row r="221" spans="1:1">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" s="12"/>
     </row>
-    <row r="222" spans="1:1">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" s="12"/>
     </row>
-    <row r="223" spans="1:1">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" s="12"/>
     </row>
-    <row r="224" spans="1:1">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" s="12"/>
     </row>
-    <row r="225" spans="1:1">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" s="12"/>
     </row>
-    <row r="226" spans="1:1">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" s="12"/>
     </row>
-    <row r="227" spans="1:1">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227" s="12"/>
     </row>
-    <row r="228" spans="1:1">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" s="12"/>
     </row>
-    <row r="229" spans="1:1">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" s="12"/>
     </row>
-    <row r="230" spans="1:1">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" s="12"/>
     </row>
-    <row r="231" spans="1:1">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" s="12"/>
     </row>
-    <row r="232" spans="1:1">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" s="12"/>
     </row>
-    <row r="233" spans="1:1">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233" s="12"/>
     </row>
-    <row r="234" spans="1:1">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" s="12"/>
     </row>
-    <row r="235" spans="1:1">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" s="12"/>
     </row>
-    <row r="236" spans="1:1">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" s="12"/>
     </row>
-    <row r="237" spans="1:1">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" s="12"/>
     </row>
-    <row r="238" spans="1:1">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" s="12"/>
     </row>
-    <row r="239" spans="1:1">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" s="12"/>
     </row>
-    <row r="240" spans="1:1">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240" s="12"/>
     </row>
-    <row r="241" spans="1:1">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" s="12"/>
     </row>
-    <row r="242" spans="1:1">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" s="12"/>
     </row>
-    <row r="243" spans="1:1">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243" s="12"/>
     </row>
-    <row r="244" spans="1:1">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244" s="12"/>
     </row>
-    <row r="245" spans="1:1">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" s="12"/>
     </row>
-    <row r="246" spans="1:1">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" s="12"/>
     </row>
-    <row r="247" spans="1:1">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247" s="12"/>
     </row>
-    <row r="248" spans="1:1">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248" s="12"/>
     </row>
-    <row r="249" spans="1:1">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249" s="12"/>
     </row>
-    <row r="250" spans="1:1">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" s="12"/>
     </row>
-    <row r="251" spans="1:1">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" s="12"/>
     </row>
-    <row r="252" spans="1:1">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" s="12"/>
     </row>
-    <row r="253" spans="1:1">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" s="12"/>
     </row>
-    <row r="254" spans="1:1">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254" s="12"/>
     </row>
-    <row r="255" spans="1:1">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A255" s="12"/>
     </row>
-    <row r="256" spans="1:1">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" s="12"/>
     </row>
-    <row r="257" spans="1:1">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257" s="12"/>
     </row>
-    <row r="258" spans="1:1">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258" s="12"/>
     </row>
-    <row r="259" spans="1:1">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" s="12"/>
     </row>
-    <row r="260" spans="1:1">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260" s="12"/>
     </row>
-    <row r="261" spans="1:1">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261" s="12"/>
     </row>
-    <row r="262" spans="1:1">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" s="12"/>
     </row>
-    <row r="263" spans="1:1">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263" s="12"/>
     </row>
-    <row r="264" spans="1:1">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264" s="12"/>
     </row>
-    <row r="265" spans="1:1">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265" s="12"/>
     </row>
-    <row r="266" spans="1:1">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266" s="12"/>
     </row>
-    <row r="267" spans="1:1">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267" s="12"/>
     </row>
-    <row r="268" spans="1:1">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268" s="12"/>
     </row>
-    <row r="269" spans="1:1">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269" s="12"/>
     </row>
-    <row r="270" spans="1:1">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270" s="12"/>
     </row>
-    <row r="271" spans="1:1">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271" s="12"/>
     </row>
-    <row r="272" spans="1:1">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272" s="12"/>
     </row>
-    <row r="273" spans="1:1">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273" s="12"/>
     </row>
-    <row r="274" spans="1:1">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A274" s="12"/>
     </row>
-    <row r="275" spans="1:1">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275" s="12"/>
     </row>
-    <row r="276" spans="1:1">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276" s="12"/>
     </row>
-    <row r="277" spans="1:1">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277" s="12"/>
     </row>
-    <row r="278" spans="1:1">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278" s="12"/>
     </row>
-    <row r="279" spans="1:1">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A279" s="12"/>
     </row>
-    <row r="280" spans="1:1">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A280" s="12"/>
     </row>
-    <row r="281" spans="1:1">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281" s="12"/>
     </row>
-    <row r="282" spans="1:1">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A282" s="12"/>
     </row>
-    <row r="283" spans="1:1">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A283" s="12"/>
     </row>
-    <row r="284" spans="1:1">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284" s="12"/>
     </row>
-    <row r="285" spans="1:1">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A285" s="12"/>
     </row>
-    <row r="286" spans="1:1">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286" s="12"/>
     </row>
-    <row r="287" spans="1:1">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A287" s="12"/>
     </row>
-    <row r="288" spans="1:1">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288" s="12"/>
     </row>
-    <row r="289" spans="1:1">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A289" s="12"/>
     </row>
-    <row r="290" spans="1:1">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290" s="12"/>
     </row>
-    <row r="291" spans="1:1">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A291" s="12"/>
     </row>
-    <row r="292" spans="1:1">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A292" s="12"/>
     </row>
-    <row r="293" spans="1:1">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293" s="12"/>
     </row>
-    <row r="294" spans="1:1">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A294" s="12"/>
     </row>
-    <row r="295" spans="1:1">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A295" s="12"/>
     </row>
-    <row r="296" spans="1:1">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A296" s="12"/>
     </row>
-    <row r="297" spans="1:1">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297" s="12"/>
     </row>
-    <row r="298" spans="1:1">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298" s="12"/>
     </row>
-    <row r="299" spans="1:1">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A299" s="12"/>
     </row>
-    <row r="300" spans="1:1">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A300" s="12"/>
     </row>
-    <row r="301" spans="1:1">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A301" s="12"/>
     </row>
-    <row r="302" spans="1:1">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A302" s="12"/>
     </row>
-    <row r="303" spans="1:1">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A303" s="12"/>
     </row>
-    <row r="304" spans="1:1">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A304" s="12"/>
     </row>
-    <row r="305" spans="1:1">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A305" s="12"/>
     </row>
-    <row r="306" spans="1:1">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A306" s="12"/>
     </row>
-    <row r="307" spans="1:1">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A307" s="12"/>
     </row>
-    <row r="308" spans="1:1">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A308" s="12"/>
     </row>
-    <row r="309" spans="1:1">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A309" s="12"/>
     </row>
-    <row r="310" spans="1:1">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A310" s="12"/>
     </row>
-    <row r="311" spans="1:1">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A311" s="12"/>
     </row>
-    <row r="312" spans="1:1">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A312" s="12"/>
     </row>
-    <row r="313" spans="1:1">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A313" s="12"/>
     </row>
-    <row r="314" spans="1:1">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A314" s="12"/>
     </row>
-    <row r="315" spans="1:1">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A315" s="12"/>
     </row>
-    <row r="316" spans="1:1">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A316" s="12"/>
     </row>
-    <row r="317" spans="1:1">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A317" s="12"/>
     </row>
-    <row r="318" spans="1:1">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A318" s="12"/>
     </row>
-    <row r="319" spans="1:1">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A319" s="12"/>
     </row>
-    <row r="320" spans="1:1">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A320" s="12"/>
     </row>
-    <row r="321" spans="1:1">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321" s="12"/>
     </row>
-    <row r="322" spans="1:1">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322" s="12"/>
     </row>
-    <row r="323" spans="1:1">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323" s="12"/>
     </row>
-    <row r="324" spans="1:1">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324" s="12"/>
     </row>
-    <row r="325" spans="1:1">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325" s="12"/>
     </row>
-    <row r="326" spans="1:1">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326" s="12"/>
     </row>
-    <row r="327" spans="1:1">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327" s="12"/>
     </row>
-    <row r="328" spans="1:1">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328" s="12"/>
     </row>
-    <row r="329" spans="1:1">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A329" s="12"/>
     </row>
-    <row r="330" spans="1:1">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A330" s="12"/>
     </row>
-    <row r="331" spans="1:1">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A331" s="12"/>
     </row>
-    <row r="332" spans="1:1">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A332" s="12"/>
     </row>
-    <row r="333" spans="1:1">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A333" s="12"/>
     </row>
-    <row r="334" spans="1:1">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A334" s="12"/>
     </row>
-    <row r="335" spans="1:1">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A335" s="13"/>
     </row>
   </sheetData>
@@ -2765,12 +2681,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="52.875" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="52.88671875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
@@ -2778,7 +2694,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
@@ -2786,7 +2702,7 @@
         <v>43229</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="67.5">
+    <row r="3" spans="1:2" ht="69" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestorsHoldInfoRegistAll.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestorsHoldInfoRegistAll.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
   <si>
     <t>2.必填要素请参照《数据元规范》。</t>
   </si>
@@ -706,10 +706,6 @@
   </si>
   <si>
     <t>折算人民币金额（元）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -894,7 +890,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
@@ -936,7 +932,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1282,10 +1281,22 @@
       </c>
       <c r="O1"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>201</v>
-      </c>
+    <row r="2" spans="1:15" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
